--- a/templates/07_Inventory.xlsx
+++ b/templates/07_Inventory.xlsx
@@ -425,14 +425,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -471,20 +471,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SKU-A30</t>
+          <t>SKU-A10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>INV-LOT-001</t>
+          <t>LOT-2026-NEW-001</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -492,153 +492,63 @@
           <t>2027-06-01</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Excess from SO-2025-099</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SKU-A30</t>
+          <t>SKU-B04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>INV-LOT-002</t>
+          <t>LOT-2026-NEW-002</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Cancelled order stock</t>
-        </is>
-      </c>
+          <t>2027-12-10</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SKU-B25</t>
+          <t>SKU-C30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INV-LOT-003</t>
+          <t>LOT-2026-NEW-003</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2027-03-01</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Overproduction</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SKU-D01</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>INV-LOT-004</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>300</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2027-12-01</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SKU-A10</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>INV-LOT-005</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>120</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2027-04-15</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>New stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SKU-C30</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>INV-LOT-006</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>50</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2027-08-01</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>Short expiry</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
